--- a/output/graficos_envejecimiento/plot_regional_d_enveje_a_2021_tarapaca_provincial.xlsx
+++ b/output/graficos_envejecimiento/plot_regional_d_enveje_a_2021_tarapaca_provincial.xlsx
@@ -39,7 +39,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 23:07</t>
+    <t xml:space="preserve">2026-10-05 05:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Region de Tarapaca</t>
+    <t xml:space="preserve">Region de Tarapacá</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
